--- a/translators/translator_bec_at_v2.0.0.xlsx
+++ b/translators/translator_bec_at_v2.0.0.xlsx
@@ -10,7 +10,6 @@
   <sheets>
     <sheet name="General Information" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="OpenBDFBuildingElementClassific" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="OpenBDFMaterialClassification" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="476">
   <si>
     <t xml:space="preserve">Field code in your format</t>
   </si>
@@ -1450,132 +1449,6 @@
   </si>
   <si>
     <t xml:space="preserve">5C Mobile Ausstattungen, Leitsysteme, Kunstwerke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bio-based materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bio-based insulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other bio-based materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plastics (PC, PE, PP, PU, PVC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fossil-based materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fossil-based insulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other fossil energy materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aluminum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brass, copper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other metal materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">g2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-metallic minerals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concrete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">q9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mineral insulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other non-metallic minerals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unbekannt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Undefined materials</t>
   </si>
 </sst>
 </file>
@@ -4597,339 +4470,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="3" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="140"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>496</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>517</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/translators/translator_bec_at_v2.0.0.xlsx
+++ b/translators/translator_bec_at_v2.0.0.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -77,6 +77,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002B5B47"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -122,7 +137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -145,6 +160,7 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -178,7 +194,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -233,6 +249,9 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,96 +512,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="85" customWidth="1" style="12" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>OpenBDF – Open Building Data Format</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Version 2.0.0 | October 2026 | pre-validation</t>
-        </is>
-      </c>
-    </row>
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>OpenBDF - Open Building Data Format</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="9" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>OpenBDF is pre-existing intellectual property of the Global Building Data</t>
-        </is>
-      </c>
-    </row>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Version 2.0.0 | October 2026 | pre-release</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Initiative (GBDI) at EPFL. It remains the property of GBDI.</t>
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>OpenBDF is developed by the team of GBDI Global Building Data Initiative at EPFL</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n"/>
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>and RISE with technical support from EPFL ENAC-IT4R. This version is shared for</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>This version is shared for expert review ahead of the November 2026 workshops</t>
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>expert review and is not yet validated. Any licence to use it is non-exclusive</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>and is not yet validated. Any licence to use it is non-exclusive and limited to</t>
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>and limited to the purpose for which it was shared. While we welcome feedback</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>the purpose for which it was shared. Material changes to the specification are</t>
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>and proposals to evolve the format, material changes to the specification are to</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>to be agreed with GBDI before they are made, so that the format is not split before it is consolidated.</t>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>be agreed with GBDI before they are published, so that the format remains</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Author: Dr Eng. Nicole Di Santo, Technical Lead, GBDI, LMC, EPFL, Lausanne.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>coherent and adjustments can be consolidated ahead of releases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Parser and code implementation: ENAC-IT4R, EPFL, Lausanne</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code repository: https://github.com/EPFL-ENAC/lmc-openbdf/ </t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Authors: Nicole Di Santo¹, Martin Röck²</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Contributors: Karen Scrivener¹, Vanderley John³, Zuhaib Batra¹</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1. GBDI Global Building Data Initiative, EPFL LMC, Lausanne, Switzerland</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2. RISE Institute for Regenerative Spatial Systems Science, Vienna, Austria</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3. University of São Paulo, São Paulo, Brazil</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Contacts:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>nicole.disanto@epfl.ch</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>martin.roeck@riselabs.at</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Parser and code implementation with support of ENAC-IT4R, EPFL, Lausanne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GitHub repository:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>https://github.com/EPFL-ENAC/lmc-openbdf/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
